--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -21,60 +21,69 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
   <x:si>
+    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
+  </x:si>
+  <x:si>
     <x:t>일반적인 테이크 다운이 아닌 상대와 몸을 붙인 클린치 상태에서 행하는 유도식 테이크 다운이다. 안다리, 밭다리 후리기, 어깨로 메치기 등이 있다. 일반적인 테이크다운보다 스태미너 소모가 적다.</x:t>
   </x:si>
   <x:si>
+    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잽</x:t>
+  </x:si>
+  <x:si>
     <x:t>엘보우</x:t>
   </x:si>
   <x:si>
+    <x:t>스윕</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파운딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로우킥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하이킥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
     <x:t>미들킥</x:t>
   </x:si>
   <x:si>
-    <x:t>하이킥</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스윕</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파운딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어퍼컷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>로우킥</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_takedown_judo</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_back_control</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_clinch_entry</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guillotine</x:t>
+  </x:si>
+  <x:si>
     <x:t>RequiredUnlockIds</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_back_control</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_clinch_entry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guillotine</x:t>
+    <x:t>skill_clinch_escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_guard_pass</x:t>
   </x:si>
   <x:si>
     <x:t>DamageMultiplier</x:t>
   </x:si>
   <x:si>
-    <x:t>skill_clinch_escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_guard_pass</x:t>
-  </x:si>
-  <x:si>
     <x:t>skill_ground_escape</x:t>
   </x:si>
   <x:si>
@@ -87,73 +96,166 @@
     <x:t>skill_kick_middle</x:t>
   </x:si>
   <x:si>
-    <x:t>매우 가까운 거리에서 팔꿈치로 상대를 가격하는 공격이다. 유효타가 적중하면 상당한 데미지를 입힌다. 스탠딩, 그라운드, 클린치 상황 등 매우 다양한 상황에서 유용하게 쓰인다.</x:t>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 태클</x:t>
+  </x:si>
+  <x:si>
+    <x:t>백 컨트롤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 탈출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Escape</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길로틴 초크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Strike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>베이스성공확률</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클린치 시도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
   </x:si>
   <x:si>
     <x:t>상대의 하체를 공략하여 그라운드로 끌고가는 기본적인 테이크다운이다.</x:t>
   </x:si>
   <x:si>
-    <x:t>상대의 클린치 컨트롤에서 빠져나와 스탠딩 상황으로 돌아간다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 거리를 좁혀 케이지 또는 근거리 클린치 공방으로 진입한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상대와 근접한 거리에서 턱이나 명치 부근을 주먹으로 올려 치는 타격이다.</x:t>
+    <x:t>Submission</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하프 가드 패스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_elbow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ActionType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCost</x:t>
   </x:si>
   <x:si>
     <x:t>Takedown</x:t>
   </x:si>
   <x:si>
+    <x:t>ClinchEntry</x:t>
+  </x:si>
+  <x:si>
     <x:t>Wrestling</x:t>
   </x:si>
   <x:si>
+    <x:t>HalfGuard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>간결하고 빠른 잽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유도식 테이크다운</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BackControl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CoolTime</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_jab</x:t>
   </x:si>
   <x:si>
-    <x:t>StaminaCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ActionType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유도식 테이크다운</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HalfGuard</x:t>
-  </x:si>
-  <x:si>
     <x:t>기술 데미지 배율</x:t>
   </x:si>
   <x:si>
     <x:t>Category</x:t>
   </x:si>
   <x:si>
-    <x:t>간결하고 빠른 잽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ClinchEntry</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BackControl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CoolTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하프 가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Submission</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_elbow</x:t>
+    <x:t>cond_standing_offense_50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_wrestling_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_standing_offense_150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_jiujitsu_offense_200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SubmissionDamageMultiplier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsBasicSkill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinUseDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_low</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GroundStrike</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxUseDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_uppercut</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_kick_high</x:t>
   </x:si>
   <x:si>
     <x:t>ChangeTopBottom</x:t>
@@ -162,121 +264,19 @@
     <x:t>PositionChange</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxUseDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsBasicSkill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_kick_low</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_uppercut</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinUseDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GroundStrike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_kick_high</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 혹은 태클 방어할 때 유효한 서브미션 기술이다. 주로 가드 포지션과 클린치 상황에서 사용한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>베이스성공확률</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클린치 시도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가드 패스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>백 컨트롤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Guard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길로틴 초크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 태클</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 탈출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Escape</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_wrestling_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_standing_offense_150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_jiujitsu_offense_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그라운드 상황에서 상대에게 타격을 가하는 공격이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SubmissionDamageMultiplier</x:t>
+    <x:t>TargetGroundPosition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_halfguard_pass</x:t>
+  </x:si>
+  <x:si>
+    <x:t>skill_ground_pounding</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StaminaCostPerSecond</x:t>
   </x:si>
   <x:si>
     <x:t>skill_takedown_basic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_ground_pounding</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StaminaCostPerSecond</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_halfguard_pass</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TargetGroundPosition</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1065,66 +1065,66 @@
   <x:sheetData>
     <x:row r="1" spans="1:14" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:17" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="P2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="Q2" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:17" s="7" customFormat="1" ht="15.75" customHeight="1">
@@ -1132,69 +1132,69 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>37</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>35</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>51</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K3" s="7" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L3" s="7" t="s">
-        <x:v>48</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="M3" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N3" s="7" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="O3" s="7" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="P3" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q3" s="7" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>2</x:v>
@@ -1212,7 +1212,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K4" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L4" s="4" t="b">
         <x:v>1</x:v>
@@ -1224,7 +1224,7 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P4" s="1" t="b">
         <x:v>0</x:v>
@@ -1235,19 +1235,19 @@
     </x:row>
     <x:row r="5" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>10</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K5" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L5" s="1" t="b">
         <x:v>0</x:v>
@@ -1277,7 +1277,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P5" s="1" t="b">
         <x:v>0</x:v>
@@ -1288,19 +1288,19 @@
     </x:row>
     <x:row r="6" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>3</x:v>
@@ -1312,13 +1312,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I6" s="1">
-        <x:v>0.59999999999999998</x:v>
+        <x:v>0.17999999999999999</x:v>
       </x:c>
       <x:c r="J6" s="1">
-        <x:v>0.90000000000000002</x:v>
+        <x:v>0.29999999999999999</x:v>
       </x:c>
       <x:c r="K6" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L6" s="1" t="b">
         <x:v>0</x:v>
@@ -1330,7 +1330,7 @@
         <x:v>1.3999999999999999</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P6" s="1" t="b">
         <x:v>0</x:v>
@@ -1341,19 +1341,19 @@
     </x:row>
     <x:row r="7" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>4</x:v>
@@ -1365,13 +1365,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="1">
-        <x:v>0.59999999999999998</x:v>
+        <x:v>0.20000000000000001</x:v>
       </x:c>
       <x:c r="J7" s="1">
-        <x:v>1.1000000000000001</x:v>
+        <x:v>0.34000000000000002</x:v>
       </x:c>
       <x:c r="K7" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L7" s="1" t="b">
         <x:v>0</x:v>
@@ -1383,7 +1383,7 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P7" s="1" t="b">
         <x:v>0</x:v>
@@ -1394,19 +1394,19 @@
     </x:row>
     <x:row r="8" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>10</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L8" s="1" t="b">
         <x:v>0</x:v>
@@ -1436,7 +1436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P8" s="1" t="b">
         <x:v>0</x:v>
@@ -1447,19 +1447,19 @@
     </x:row>
     <x:row r="9" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>6</x:v>
@@ -1471,13 +1471,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I9" s="1">
-        <x:v>0.59999999999999998</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="J9" s="1">
-        <x:v>1.1000000000000001</x:v>
+        <x:v>0.40000000000000002</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L9" s="1" t="b">
         <x:v>0</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P9" s="1" t="b">
         <x:v>0</x:v>
@@ -1500,19 +1500,19 @@
     </x:row>
     <x:row r="10" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>2</x:v>
@@ -1524,13 +1524,13 @@
         <x:v>0.69999999999999996</x:v>
       </x:c>
       <x:c r="I10" s="1">
-        <x:v>0.90000000000000002</x:v>
+        <x:v>0.28000000000000003</x:v>
       </x:c>
       <x:c r="J10" s="1">
-        <x:v>1.8</x:v>
+        <x:v>0.46000000000000002</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L10" s="1" t="b">
         <x:v>1</x:v>
@@ -1542,7 +1542,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P10" s="1" t="b">
         <x:v>0</x:v>
@@ -1553,19 +1553,19 @@
     </x:row>
     <x:row r="11" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>3</x:v>
@@ -1577,13 +1577,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="1">
-        <x:v>0.59999999999999998</x:v>
+        <x:v>0.17999999999999999</x:v>
       </x:c>
       <x:c r="J11" s="1">
-        <x:v>0.90000000000000002</x:v>
+        <x:v>0.29999999999999999</x:v>
       </x:c>
       <x:c r="K11" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L11" s="1" t="b">
         <x:v>0</x:v>
@@ -1595,7 +1595,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O11" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P11" s="1" t="b">
         <x:v>0</x:v>
@@ -1606,19 +1606,19 @@
     </x:row>
     <x:row r="12" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>3</x:v>
@@ -1636,7 +1636,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L12" s="1" t="b">
         <x:v>1</x:v>
@@ -1648,7 +1648,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P12" s="1" t="b">
         <x:v>0</x:v>
@@ -1659,19 +1659,19 @@
     </x:row>
     <x:row r="13" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>4</x:v>
@@ -1689,7 +1689,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L13" s="1" t="b">
         <x:v>1</x:v>
@@ -1701,7 +1701,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="P13" s="1" t="b">
         <x:v>0</x:v>
@@ -1712,19 +1712,19 @@
     </x:row>
     <x:row r="14" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F14" s="1">
         <x:v>5</x:v>
@@ -1742,7 +1742,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L14" s="1" t="b">
         <x:v>1</x:v>
@@ -1754,7 +1754,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O14" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="P14" s="1" t="b">
         <x:v>0</x:v>
@@ -1765,19 +1765,19 @@
     </x:row>
     <x:row r="15" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>5</x:v>
@@ -1795,7 +1795,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L15" s="1" t="b">
         <x:v>1</x:v>
@@ -1807,7 +1807,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="P15" s="1" t="b">
         <x:v>0</x:v>
@@ -1818,19 +1818,19 @@
     </x:row>
     <x:row r="16" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F16" s="1">
         <x:v>5</x:v>
@@ -1848,7 +1848,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K16" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L16" s="1" t="b">
         <x:v>1</x:v>
@@ -1860,7 +1860,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="P16" s="1" t="b">
         <x:v>1</x:v>
@@ -1871,19 +1871,19 @@
     </x:row>
     <x:row r="17" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>5</x:v>
@@ -1901,7 +1901,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L17" s="1" t="b">
         <x:v>1</x:v>
@@ -1913,7 +1913,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P17" s="1" t="b">
         <x:v>0</x:v>
@@ -1924,19 +1924,19 @@
     </x:row>
     <x:row r="18" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A18" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F18" s="1">
         <x:v>8</x:v>
@@ -1948,13 +1948,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I18" s="1">
-        <x:v>1.8</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="J18" s="1">
-        <x:v>2.7999999999999998</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="K18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L18" s="1" t="b">
         <x:v>1</x:v>
@@ -1966,7 +1966,7 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="O18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P18" s="1" t="b">
         <x:v>0</x:v>
@@ -1977,19 +1977,19 @@
     </x:row>
     <x:row r="19" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A19" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>5</x:v>
@@ -2001,13 +2001,13 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="I19" s="1">
-        <x:v>1</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="J19" s="1">
-        <x:v>2</x:v>
+        <x:v>0.47999999999999998</x:v>
       </x:c>
       <x:c r="K19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L19" s="1" t="b">
         <x:v>0</x:v>
@@ -2019,7 +2019,7 @@
         <x:v>0.59999999999999998</x:v>
       </x:c>
       <x:c r="O19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P19" s="1" t="b">
         <x:v>0</x:v>
@@ -2030,19 +2030,19 @@
     </x:row>
     <x:row r="20" spans="1:17" ht="15.75" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F20" s="1">
         <x:v>6</x:v>
@@ -2054,13 +2054,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I20" s="1">
-        <x:v>1.3</x:v>
+        <x:v>0.32000000000000001</x:v>
       </x:c>
       <x:c r="J20" s="1">
-        <x:v>2.7999999999999998</x:v>
+        <x:v>0.57999999999999996</x:v>
       </x:c>
       <x:c r="K20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L20" s="1" t="b">
         <x:v>0</x:v>
@@ -2072,7 +2072,7 @@
         <x:v>1.8</x:v>
       </x:c>
       <x:c r="O20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P20" s="1" t="b">
         <x:v>0</x:v>
